--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
@@ -565,13 +565,13 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>92.91030000000001</v>
+        <v>74.6788</v>
       </c>
       <c r="E2" t="n">
-        <v>60.656</v>
+        <v>46.8271</v>
       </c>
       <c r="F2" t="n">
-        <v>32.2544</v>
+        <v>27.8521</v>
       </c>
       <c r="G2" t="n">
         <v>12.3383</v>
@@ -610,13 +610,13 @@
         <v>41.1366</v>
       </c>
       <c r="S2" t="n">
-        <v>41.9577</v>
+        <v>23.7266</v>
       </c>
       <c r="T2" t="n">
-        <v>29.3718</v>
+        <v>15.5424</v>
       </c>
       <c r="U2" t="n">
-        <v>12.5861</v>
+        <v>8.1839</v>
       </c>
       <c r="V2" t="n">
         <v>32.3867</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>82.3038</v>
+        <v>66.9888</v>
       </c>
       <c r="E3" t="n">
-        <v>54.6411</v>
+        <v>37.7316</v>
       </c>
       <c r="F3" t="n">
-        <v>27.6627</v>
+        <v>29.2575</v>
       </c>
       <c r="G3" t="n">
         <v>35.8402</v>
@@ -688,13 +688,13 @@
         <v>48.3072</v>
       </c>
       <c r="S3" t="n">
-        <v>35.8337</v>
+        <v>20.5184</v>
       </c>
       <c r="T3" t="n">
-        <v>32.0534</v>
+        <v>15.1433</v>
       </c>
       <c r="U3" t="n">
-        <v>3.7801</v>
+        <v>5.3751</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144999999999996</v>
@@ -721,13 +721,13 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>70.077</v>
+        <v>61.9031</v>
       </c>
       <c r="E4" t="n">
-        <v>44.3865</v>
+        <v>38.134</v>
       </c>
       <c r="F4" t="n">
-        <v>25.6902</v>
+        <v>23.7693</v>
       </c>
       <c r="G4" t="n">
         <v>34.5279</v>
@@ -766,13 +766,13 @@
         <v>26.7954</v>
       </c>
       <c r="S4" t="n">
-        <v>24.9176</v>
+        <v>16.7438</v>
       </c>
       <c r="T4" t="n">
-        <v>17.5773</v>
+        <v>11.3246</v>
       </c>
       <c r="U4" t="n">
-        <v>7.3403</v>
+        <v>5.4193</v>
       </c>
       <c r="V4" t="n">
         <v>1.0076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>29.8694</v>
+        <v>35.5521</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9413</v>
+        <v>-2.406300000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>17.9284</v>
+        <v>37.9583</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6877</v>
+        <v>7.268999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-11.1302</v>
+        <v>14.4376</v>
       </c>
       <c r="I5" t="n">
-        <v>9.442300000000001</v>
+        <v>-7.168500000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.934600000000001</v>
+        <v>20.9264</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.5129</v>
+        <v>30.0733</v>
       </c>
       <c r="L5" t="n">
-        <v>7.447299999999999</v>
+        <v>-9.146700000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6224</v>
+        <v>-13.6574</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.6173</v>
+        <v>-15.6354</v>
       </c>
       <c r="O5" t="n">
-        <v>1.995</v>
+        <v>1.9781</v>
       </c>
       <c r="P5" t="n">
-        <v>6.038399999999999</v>
+        <v>13.7751</v>
       </c>
       <c r="Q5" t="n">
-        <v>-13.7751</v>
+        <v>-42.2688</v>
       </c>
       <c r="R5" t="n">
-        <v>19.8135</v>
+        <v>56.0439</v>
       </c>
       <c r="S5" t="n">
-        <v>23.0665</v>
+        <v>6.8016</v>
       </c>
       <c r="T5" t="n">
-        <v>13.5565</v>
+        <v>1.7309</v>
       </c>
       <c r="U5" t="n">
-        <v>9.5101</v>
+        <v>5.071000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4524</v>
+        <v>7.7064</v>
       </c>
       <c r="W5" t="n">
-        <v>9.225</v>
+        <v>17.2048</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.772600000000001</v>
+        <v>-9.4985</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>23.8294</v>
+        <v>32.6825</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3727999999999989</v>
+        <v>19.2937</v>
       </c>
       <c r="F6" t="n">
-        <v>24.2024</v>
+        <v>13.3887</v>
       </c>
       <c r="G6" t="n">
-        <v>8.721400000000001</v>
+        <v>16.7083</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9502</v>
+        <v>0.4108999999999996</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.2287</v>
+        <v>16.2968</v>
       </c>
       <c r="J6" t="n">
-        <v>13.8536</v>
+        <v>32.5089</v>
       </c>
       <c r="K6" t="n">
-        <v>16.2854</v>
+        <v>12.0837</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.4321</v>
+        <v>20.425</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.132000000000001</v>
+        <v>-15.8009</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.3352</v>
+        <v>-11.6726</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7968999999999997</v>
+        <v>-4.1282</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.2079</v>
+        <v>16.6056</v>
       </c>
       <c r="Q6" t="n">
-        <v>-30.5694</v>
+        <v>-23.5875</v>
       </c>
       <c r="R6" t="n">
-        <v>27.3615</v>
+        <v>40.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>17.2605</v>
+        <v>9.229099999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>9.4015</v>
+        <v>5.2986</v>
       </c>
       <c r="U6" t="n">
-        <v>7.8592</v>
+        <v>3.930400000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.055300000000001</v>
+        <v>-9.860300000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9415</v>
+        <v>5.073600000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.886200000000001</v>
+        <v>-14.9339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>20.4515</v>
+        <v>26.6851</v>
       </c>
       <c r="E7" t="n">
-        <v>8.091200000000001</v>
+        <v>-3.5466</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3598</v>
+        <v>30.2316</v>
       </c>
       <c r="G7" t="n">
-        <v>11.7427</v>
+        <v>-4.5129</v>
       </c>
       <c r="H7" t="n">
-        <v>9.693900000000001</v>
+        <v>9.3569</v>
       </c>
       <c r="I7" t="n">
-        <v>2.049</v>
+        <v>-13.8695</v>
       </c>
       <c r="J7" t="n">
-        <v>14.8251</v>
+        <v>1.823399999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>15.3564</v>
+        <v>20.5695</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5316000000000003</v>
+        <v>-18.746</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.082</v>
+        <v>-6.3363</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.6625</v>
+        <v>-11.2126</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5802</v>
+        <v>4.8762</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6418</v>
+        <v>20.1909</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.5683</v>
+        <v>-22.0779</v>
       </c>
       <c r="R7" t="n">
-        <v>23.2101</v>
+        <v>42.2688</v>
       </c>
       <c r="S7" t="n">
-        <v>5.6437</v>
+        <v>9.7654</v>
       </c>
       <c r="T7" t="n">
-        <v>5.835500000000001</v>
+        <v>7.1241</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1918</v>
+        <v>2.6413</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4228999999999996</v>
+        <v>1.2419</v>
       </c>
       <c r="W7" t="n">
-        <v>7.9988</v>
+        <v>9.5838</v>
       </c>
       <c r="X7" t="n">
-        <v>-7.5759</v>
+        <v>-8.341900000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>18.4966</v>
+        <v>21.156</v>
       </c>
       <c r="E8" t="n">
-        <v>5.940399999999999</v>
+        <v>5.1225</v>
       </c>
       <c r="F8" t="n">
-        <v>12.5561</v>
+        <v>16.0336</v>
       </c>
       <c r="G8" t="n">
-        <v>16.7083</v>
+        <v>-1.6877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4108999999999996</v>
+        <v>-11.1302</v>
       </c>
       <c r="I8" t="n">
-        <v>16.2968</v>
+        <v>9.442300000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>32.5089</v>
+        <v>2.934600000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.0837</v>
+        <v>-4.5129</v>
       </c>
       <c r="L8" t="n">
-        <v>20.425</v>
+        <v>7.447299999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-15.8009</v>
+        <v>-4.6224</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.6726</v>
+        <v>-6.6173</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.1282</v>
+        <v>1.995</v>
       </c>
       <c r="P8" t="n">
-        <v>16.6056</v>
+        <v>6.038399999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-23.5875</v>
+        <v>-13.7751</v>
       </c>
       <c r="R8" t="n">
-        <v>40.1931</v>
+        <v>19.8135</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.9566</v>
+        <v>14.353</v>
       </c>
       <c r="T8" t="n">
-        <v>-8.0547</v>
+        <v>6.7377</v>
       </c>
       <c r="U8" t="n">
-        <v>3.098100000000001</v>
+        <v>7.6152</v>
       </c>
       <c r="V8" t="n">
-        <v>-9.860300000000001</v>
+        <v>2.4524</v>
       </c>
       <c r="W8" t="n">
-        <v>5.073600000000001</v>
+        <v>9.225</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.9339</v>
+        <v>-6.772600000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>14.7333</v>
+        <v>19.7632</v>
       </c>
       <c r="E9" t="n">
-        <v>-12.5538</v>
+        <v>5.757899999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>27.2873</v>
+        <v>14.0054</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5129</v>
+        <v>11.7427</v>
       </c>
       <c r="H9" t="n">
-        <v>9.3569</v>
+        <v>9.693900000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.8695</v>
+        <v>2.049</v>
       </c>
       <c r="J9" t="n">
-        <v>1.823399999999999</v>
+        <v>14.8251</v>
       </c>
       <c r="K9" t="n">
-        <v>20.5695</v>
+        <v>15.3564</v>
       </c>
       <c r="L9" t="n">
-        <v>-18.746</v>
+        <v>-0.5316000000000003</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.3363</v>
+        <v>-3.082</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.2126</v>
+        <v>-5.6625</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8762</v>
+        <v>2.5802</v>
       </c>
       <c r="P9" t="n">
-        <v>20.1909</v>
+        <v>2.6418</v>
       </c>
       <c r="Q9" t="n">
-        <v>-22.0779</v>
+        <v>-20.5683</v>
       </c>
       <c r="R9" t="n">
-        <v>42.2688</v>
+        <v>23.2101</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1863</v>
+        <v>4.9557</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.8833</v>
+        <v>3.5021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3026999999999999</v>
+        <v>1.4536</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2419</v>
+        <v>0.4228999999999996</v>
       </c>
       <c r="W9" t="n">
-        <v>9.5838</v>
+        <v>7.9988</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.341900000000001</v>
+        <v>-7.5759</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>9.676600000000001</v>
+        <v>19.48</v>
       </c>
       <c r="E10" t="n">
-        <v>-22.7547</v>
+        <v>-2.8828</v>
       </c>
       <c r="F10" t="n">
-        <v>32.4311</v>
+        <v>22.3629</v>
       </c>
       <c r="G10" t="n">
-        <v>7.268999999999999</v>
+        <v>8.721400000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>14.4376</v>
+        <v>11.9502</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.168500000000001</v>
+        <v>-3.2287</v>
       </c>
       <c r="J10" t="n">
-        <v>20.9264</v>
+        <v>13.8536</v>
       </c>
       <c r="K10" t="n">
-        <v>30.0733</v>
+        <v>16.2854</v>
       </c>
       <c r="L10" t="n">
-        <v>-9.146700000000001</v>
+        <v>-2.4321</v>
       </c>
       <c r="M10" t="n">
-        <v>-13.6574</v>
+        <v>-5.132000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-15.6354</v>
+        <v>-4.3352</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9781</v>
+        <v>-0.7968999999999997</v>
       </c>
       <c r="P10" t="n">
-        <v>13.7751</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q10" t="n">
-        <v>-42.2688</v>
+        <v>-30.5694</v>
       </c>
       <c r="R10" t="n">
-        <v>56.0439</v>
+        <v>27.3615</v>
       </c>
       <c r="S10" t="n">
-        <v>-19.074</v>
+        <v>12.9111</v>
       </c>
       <c r="T10" t="n">
-        <v>-18.6176</v>
+        <v>6.8915</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4565</v>
+        <v>6.019500000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>7.7064</v>
+        <v>1.055300000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>17.2048</v>
+        <v>6.9415</v>
       </c>
       <c r="X10" t="n">
-        <v>-9.4985</v>
+        <v>-5.886200000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>7.051300000000001</v>
+        <v>10.2182</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5442</v>
+        <v>0.2039999999999997</v>
       </c>
       <c r="F11" t="n">
-        <v>9.595600000000001</v>
+        <v>10.0142</v>
       </c>
       <c r="G11" t="n">
         <v>3.5171</v>
@@ -1312,13 +1312,13 @@
         <v>10.7559</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3522000000000001</v>
+        <v>2.8146</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.6034</v>
+        <v>0.145</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2512</v>
+        <v>2.6698</v>
       </c>
       <c r="V11" t="n">
         <v>2.7542</v>
@@ -1345,13 +1345,13 @@
         <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2387</v>
+        <v>6.7211</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9501000000000001</v>
+        <v>1.4005</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2883</v>
+        <v>5.3206</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6720000000000002</v>
@@ -1390,13 +1390,13 @@
         <v>10.9446</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7125000000000001</v>
+        <v>1.77</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2293</v>
+        <v>1.6796</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9421</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.3397999999999997</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ó. GONZÁLEZ JURADO</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0528</v>
+        <v>5.1313</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0528</v>
+        <v>3.1249</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.0064</v>
       </c>
       <c r="G13" t="n">
-        <v>4.0528</v>
+        <v>0.3597</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5849</v>
+        <v>-2.0911</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4679</v>
+        <v>2.4508</v>
       </c>
       <c r="J13" t="n">
-        <v>4.0528</v>
+        <v>-0.2437</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5849</v>
+        <v>-1.5683</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4679</v>
+        <v>1.3247</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.1261</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.0735</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.0669</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.006500000000000006</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ISIDRO PENA</t>
+          <t>Ó. GONZÁLEZ JURADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3261</v>
+        <v>4.0528</v>
       </c>
       <c r="E14" t="n">
-        <v>1.897</v>
+        <v>4.0528</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4293</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3597</v>
+        <v>4.0528</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0911</v>
+        <v>1.5849</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4508</v>
+        <v>2.4679</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2437</v>
+        <v>4.0528</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5683</v>
+        <v>1.5849</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3247</v>
+        <v>2.4679</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6032999999999999</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1261</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6418</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7319</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1611</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5707</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8607</v>
+        <v>2.8434</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5386</v>
+        <v>0.3383</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3993</v>
+        <v>2.5051</v>
       </c>
       <c r="G15" t="n">
         <v>2.9951</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4173</v>
+        <v>-0.4346</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2222</v>
+        <v>-0.3453</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1951</v>
+        <v>-0.0893</v>
       </c>
       <c r="V15" t="n">
         <v>0.2828</v>
@@ -1657,13 +1657,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2707</v>
+        <v>1.6495</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6392</v>
+        <v>-1.7366</v>
       </c>
       <c r="F16" t="n">
-        <v>2.91</v>
+        <v>3.3862</v>
       </c>
       <c r="G16" t="n">
         <v>2.6862</v>
@@ -1702,13 +1702,13 @@
         <v>3.0192</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0006</v>
+        <v>-0.6217999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7614</v>
+        <v>-0.8588</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2393</v>
+        <v>0.237</v>
       </c>
       <c r="V16" t="n">
         <v>-1.547</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ANDREU TARIN</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1875</v>
+        <v>-0.7450999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5826</v>
+        <v>-5.745699999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3951</v>
+        <v>5.000299999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1511</v>
+        <v>-9.598800000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.123</v>
+        <v>-1.349299999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0281</v>
+        <v>-8.249700000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1123</v>
+        <v>-7.145</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5862000000000001</v>
+        <v>2.6435</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5262</v>
+        <v>-9.7887</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0388</v>
+        <v>-2.4537</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5369</v>
+        <v>-3.9928</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4981</v>
+        <v>1.5388</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5661</v>
+        <v>8.326672684688674e-17</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-13.209</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5661</v>
+        <v>13.209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6025</v>
+        <v>4.7594</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4703</v>
+        <v>3.1189</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1322</v>
+        <v>1.6407</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.0944</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>11.4896</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-7.3952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MEJIA SERRANO</t>
+          <t>J. ANDREU TARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1047</v>
+        <v>-0.9036</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.583</v>
+        <v>-1.1929</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4783</v>
+        <v>0.2893</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8707</v>
+        <v>-1.1511</v>
       </c>
       <c r="H19" t="n">
-        <v>4.490600000000001</v>
+        <v>-1.123</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6198</v>
+        <v>-0.0281</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2011000000000001</v>
+        <v>-1.1123</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5751</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.3739</v>
+        <v>-0.5262</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6696</v>
+        <v>-0.0388</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0844</v>
+        <v>-0.5369</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7541</v>
+        <v>0.4981</v>
       </c>
       <c r="P19" t="n">
-        <v>-5.2836</v>
+        <v>0.5661</v>
       </c>
       <c r="Q19" t="n">
-        <v>-7.9254</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9369000000000001</v>
+        <v>-0.3186</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4057</v>
+        <v>-0.0806</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5313</v>
+        <v>-0.238</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>P. MEJIA SERRANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.407</v>
+        <v>-0.9418000000000002</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.5288</v>
+        <v>-5.1584</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1215</v>
+        <v>4.2166</v>
       </c>
       <c r="G20" t="n">
-        <v>-9.598800000000001</v>
+        <v>1.8707</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.349299999999999</v>
+        <v>4.490600000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-8.249700000000001</v>
+        <v>-2.6198</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.145</v>
+        <v>0.2011000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6435</v>
+        <v>4.5751</v>
       </c>
       <c r="L20" t="n">
-        <v>-9.7887</v>
+        <v>-4.3739</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4537</v>
+        <v>1.6696</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.9928</v>
+        <v>-0.0844</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5388</v>
+        <v>1.7541</v>
       </c>
       <c r="P20" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>-5.2836</v>
       </c>
       <c r="Q20" t="n">
-        <v>-13.209</v>
+        <v>-7.9254</v>
       </c>
       <c r="R20" t="n">
-        <v>13.209</v>
+        <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9022</v>
+        <v>1.2258</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6640999999999998</v>
+        <v>1.0188</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2382</v>
+        <v>0.207</v>
       </c>
       <c r="V20" t="n">
-        <v>4.0944</v>
+        <v>1.2452</v>
       </c>
       <c r="W20" t="n">
-        <v>11.4896</v>
+        <v>1.547</v>
       </c>
       <c r="X20" t="n">
-        <v>-7.3952</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>-14.6632</v>
+        <v>-9.837300000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.222</v>
+        <v>-4.848800000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.441199999999998</v>
+        <v>-4.9886</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6009</v>
@@ -2092,13 +2092,13 @@
         <v>6.793200000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.9004</v>
+        <v>-0.07460000000000007</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.3416</v>
+        <v>-0.9683999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5588</v>
+        <v>0.8937999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-6.9731</v>
@@ -2125,13 +2125,13 @@
         <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>358.4198</v>
+        <v>377.7121</v>
       </c>
       <c r="E22" t="n">
-        <v>126.8707</v>
+        <v>135.1032</v>
       </c>
       <c r="F22" t="n">
-        <v>231.5486</v>
+        <v>242.6095</v>
       </c>
       <c r="G22" t="n">
         <v>123.04</v>
@@ -2152,7 +2152,7 @@
         <v>10.6293</v>
       </c>
       <c r="M22" t="n">
-        <v>-78.91329999999999</v>
+        <v>-78.91329999999998</v>
       </c>
       <c r="N22" t="n">
         <v>-99.75410000000001</v>
@@ -2161,7 +2161,7 @@
         <v>20.8406</v>
       </c>
       <c r="P22" t="n">
-        <v>87.93420000000002</v>
+        <v>87.93419999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-289.6545</v>
@@ -2170,13 +2170,13 @@
         <v>377.5887</v>
       </c>
       <c r="S22" t="n">
-        <v>109.9063</v>
+        <v>129.1984</v>
       </c>
       <c r="T22" t="n">
-        <v>69.83990000000001</v>
+        <v>78.07129999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>40.0664</v>
+        <v>51.1271</v>
       </c>
       <c r="V22" t="n">
         <v>37.5399</v>
